--- a/tab.xlsx
+++ b/tab.xlsx
@@ -1,64 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UnseR\Desktop\R\ARU\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="11">
-  <si>
-    <t>dis</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>base</t>
-  </si>
-  <si>
-    <t>porcentaje</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>2019</t>
-  </si>
-  <si>
-    <t>Si</t>
-  </si>
-  <si>
-    <t>2021</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>2023</t>
-  </si>
-  <si>
-    <t>2024</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,19 +63,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -160,7 +109,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -192,10 +141,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -227,7 +175,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -403,162 +350,88 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:E11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>s09a_02</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>s09a_04</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>18.90977030300654</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="C3">
+        <v>58.28088208618601</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B2">
-        <v>10520.477934979899</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="C4">
+        <v>10.10433430419575</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>1.725151581755958</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2">
-        <v>89.338297681554764</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B3">
-        <v>1255.522065020114</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3">
-        <v>10.66170231844524</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B4">
-        <v>10643.199545077559</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4">
-        <v>87.353903029198648</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5">
-        <v>1540.800454922437</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>12.64609697080135</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6">
-        <v>9695.3298673965037</v>
-      </c>
-      <c r="C6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>83.551619021242047</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7">
-        <v>1908.670128021389</v>
-      </c>
-      <c r="C7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7">
-        <v>16.448380978757939</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B8">
-        <v>10445.187804049619</v>
-      </c>
-      <c r="C8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8">
-        <v>85.030835265789804</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9">
-        <v>1838.812195950381</v>
-      </c>
-      <c r="C9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9">
-        <v>14.969164734210199</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10">
-        <v>10739.09963784814</v>
-      </c>
-      <c r="C10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10">
-        <v>85.129604739184657</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B11">
-        <v>1875.900362151855</v>
-      </c>
-      <c r="C11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11">
-        <v>14.870395260815339</v>
+      <c r="C6">
+        <v>1.519306225212044</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>1785.360917651499</v>
       </c>
     </row>
   </sheetData>
